--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4542" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,10 +263,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare plan for patient or group</t>
-  </si>
-  <si>
-    <t>Describes the intention of how one or more practitioners intend to deliver care for a particular patient, group or community for a period of time, possibly limited to care for a specific condition or set of conditions.</t>
+    <t>特定照護目標下為一位患者或一群患者識別的活動、干預和結果計畫</t>
+  </si>
+  <si>
+    <t>描述為實現一個或多個目標而將為一位患者(或一群患者)進行的活動的計畫，包括診斷、監測、評估、治療、藥物治療、追蹤等。</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -292,13 +292,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>不重複的 ID 用以識別儲存在特定 FHIR Server 中的 CarePlan 紀錄，通常又稱為邏輯性 ID。</t>
+  </si>
+  <si>
+    <t>resource 的邏輯 ID，在 resource 的 URL 中使用。一旦指定，這個值永遠不會改變。</t>
+  </si>
+  <si>
+    <t>一個 resource 使用新增操作(create operation)提交給伺服器時，此 resource 沒有 id，它的 id 在 resource 被創建後由伺器分配/指定。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -311,10 +311,10 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>此 CarePlan Resource 的 metadata</t>
+  </si>
+  <si>
+    <t>關於 resource 的 metadata。這是由基礎建設維護的內容。內容的更改可能並不總是與 resource 的版本更改相關聯。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -331,13 +331,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
+  </si>
+  <si>
+    <t>宣告這套規則限制了內容只能被有限的交易夥伴所理解。這從本質上限制了資料的長期有用性。然而，現有的健康生態體系高度分裂，還沒有準備好以普遍可計算的方式定義、收集和交換資料。只要有可能，實作者和/或規範編寫者應該避免使用這個資料項目。通常在使用時，此 URL 是對 IG 的參照，此 IG 將這些特殊規則與其他 profiles、value sets 等一起定義為其敘述的一部分。</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -350,19 +350,22 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>用以表述 CarePlan Resource 內容的語言</t>
+  </si>
+  <si>
+    <t>編寫此 resource 的語言</t>
+  </si>
+  <si>
+    <t>提供語言是為了支援索引和可存取性(通常，文字表述轉語音等服務使用此語言標籤)。html lanuage tag 適用於此敘述。resource 上的語言標籤可用於指定從 resource 中的資料所產成的其他表述之語言。不是所有的內容都必須使用此語言。不應該假定 Resource.language 自動適用於敘述。如果指定語言，它也應該被指定在 html 中的 div 資料項目(關於 xml:lang 和 html lang 屬性之間的關係，見 HTML5 中的規則)。</t>
+  </si>
+  <si>
+    <t>zh-TW</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>人類語言；鼓勵使用 CommonLanguages 代碼表中的代碼，但不強制一定要使用此代碼表，你也可使用其他代碼表的代碼或單純以文字表示。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -382,13 +385,13 @@
 </t>
   </si>
   <si>
-    <t>CarePlan Resource之內容摘要以供人閱讀</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>CarePlan Resource 之內容摘要以供人閱讀</t>
+  </si>
+  <si>
+    <t>人可讀的敘述，包含 resource 的摘要，可用於向人表述 resource 的內容。敘述不需要對所有的結構化資料進行編碼，但需要包含足夠的細節使人在閱讀敘述時理解「臨床安全性」。resource 定義有哪些內容應該在敘述中表示，以確保臨床安全。</t>
+  </si>
+  <si>
+    <t>內嵌(contained)的 resource 沒有敘述，非內嵌(contained)的 resource 則 **建議應該(SHOULD)** 有敘述。有時 resource 可能只有文字表述，很少或沒有額外的結構化資料(只要滿足所有 minOccurs=1 的資料項目)。這可能出現在舊系統的資料，當資訊以 「文字表述區塊(text blob)」的形式被取得，或者文字表述是原始輸入或說明，而編碼資訊稍後再添加。</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -465,7 +468,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Constrained value set of narrative statuses.</t>
+    <t>敘述狀態的受限值集。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/narrative-status</t>
@@ -484,7 +487,7 @@
 </t>
   </si>
   <si>
-    <t>Limited xhtml content</t>
+    <t>有限的 xhtml 內容</t>
   </si>
   <si>
     <t>The actual narrative content, a stripped down version of XHTML.</t>
@@ -582,7 +585,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -627,7 +630,10 @@
     <t>照顧計畫的來源，即這項照顧計畫是基於哪個照顧計畫？</t>
   </si>
   <si>
-    <t>A care plan that is fulfilled in whole or in part by this care plan.</t>
+    <t>識別此照護計畫所建立的父計畫。</t>
+  </si>
+  <si>
+    <t>參照可以是相對的、絕對的或內部的。</t>
   </si>
   <si>
     <t>Allows tracing of the care plan and tracking whether proposals/recommendations were acted upon.</t>
@@ -732,10 +738,7 @@
     <t>照顧計畫的替代，即這項照顧計畫已經被哪個照顧計畫替代？</t>
   </si>
   <si>
-    <t>Completed or terminated care plan whose function is taken by this new care plan.</t>
-  </si>
-  <si>
-    <t>The replacement could be because the initial care plan was immediately rejected (due to an issue) or because the previous care plan was completed, but the need for the action described by the care plan remains ongoing.</t>
+    <t>識別被此照護計畫所取代的照護計畫。</t>
   </si>
   <si>
     <t>Allows tracing the continuation of a therapy or administrative process instantiated through multiple care plans.</t>
@@ -771,10 +774,7 @@
     <t>照顧計畫的緊急備用方案，即這項照顧計畫使用哪個緊急備用方案？</t>
   </si>
   <si>
-    <t>A larger care plan of which this particular care plan is a component or step.</t>
-  </si>
-  <si>
-    <t>Each care plan is an independent request, such that having a care plan be part of another care plan can cause issues with cascading statuses.  As such, this element is still being discussed.</t>
+    <t>此照護計畫是另一個照護計畫的一部分。例如，專門針對骨折修復或糖尿病控制的計畫可能是出院護理計畫的一部分。</t>
   </si>
   <si>
     <t>CarePlan.partOf.id</t>
@@ -804,11 +804,13 @@
     <t>照顧計畫的狀態。[應填入以下字串之一：active | on-hold | completed | cancelled | entered-in-error | unknown]</t>
   </si>
   <si>
-    <t>Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
-  </si>
-  <si>
-    <t>The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the care plan.
-This element is labeled as a modifier because the status contains the code entered-in-error that marks the plan as not currently valid.</t>
+    <t>指明照護計畫是否正在執行中、表示未來意向或現在已成為歷史記錄。</t>
+  </si>
+  <si>
+    <t>可以在 [[event.html#statemachine | 事件模式]] 文件中找到一個標準的狀態轉換圖。「未知」不代表「其他」狀態 - 必須使用其中一個已定義的狀態，「未知」用於表示不確定當前狀態。</t>
+  </si>
+  <si>
+    <t>指出計畫是否正在實施、代表未來意圖或是現在的歷史記錄。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-status</t>
@@ -832,7 +834,7 @@
     <t>照顧計畫的意圖。[應填入以下字串之一：proposal | plan | order | option]</t>
   </si>
   <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+    <t>表示與照護計畫相關的權威性/意向性程度。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -841,7 +843,7 @@
     <t>Proposals/recommendations, plans and orders all use the same structure and can exist in the same fulfillment chain.</t>
   </si>
   <si>
-    <t>Codes indicating the degree of authority/intentionality associated with a care plan</t>
+    <t>表示與照護計畫相關的權威性/意向性程度的代碼</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-intent</t>
@@ -860,13 +862,13 @@
     <t>照顧計畫的分類。</t>
   </si>
   <si>
-    <t>Type of plan.</t>
+    <t>照護計畫的類型。</t>
   </si>
   <si>
     <t>There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
   </si>
   <si>
-    <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g., "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
+    <t>識別這是什麼「種類」的計畫，以支援多個共存計畫之間的區分；例如：「居家健康」、「精神科」、「氣喘」、「疾病管理」、「保健計畫」等。</t>
   </si>
   <si>
     <t>example</t>
@@ -875,7 +877,7 @@
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -891,7 +893,7 @@
     <t>AssessPlan</t>
   </si>
   <si>
-    <t>Type of plan</t>
+    <t>評估計畫</t>
   </si>
   <si>
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
@@ -946,10 +948,10 @@
     <t>照顧計畫的適用主體，即這個照顧計畫的適用對象是誰？</t>
   </si>
   <si>
-    <t>Who care plan is for.</t>
-  </si>
-  <si>
-    <t>Identifies the patient or group whose intended care is described by the plan.</t>
+    <t>照護計畫是為了誰。</t>
+  </si>
+  <si>
+    <t>識別計畫描述其意圖照護的病人或群體。</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -995,10 +997,10 @@
     <t>照顧計畫對應的就診資訊，即這個照顧計畫是哪個就診資訊的一部分？</t>
   </si>
   <si>
-    <t>The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
+    <t>此照護計畫是在哪個就醫情境產生的。</t>
+  </si>
+  <si>
+    <t>參照可以是相對的、絕對的或內部的。注意：如果 Encounter 參照是一個 Episode of Care 的一部分，則此資料點不足以隱含建立關聯。</t>
   </si>
   <si>
     <t>Request.context</t>
@@ -1160,10 +1162,7 @@
     <t>照顧計畫的提出者，即這個照顧計畫是由誰提出或計畫的？</t>
   </si>
   <si>
-    <t>When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
-  </si>
-  <si>
-    <t>The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
+    <t>負責建立照護計畫內容的個人或組織。</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1199,10 +1198,7 @@
     <t>照顧計畫的參與者，即這個照顧計畫是由誰來參與的？</t>
   </si>
   <si>
-    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
-  </si>
-  <si>
-    <t>Collaborative care plans may have multiple contributors.</t>
+    <t>對照護計畫的建立提供資訊的個人或組織，但不對照護計畫負責。</t>
   </si>
   <si>
     <t>CarePlan.contributor.id</t>
@@ -1233,10 +1229,10 @@
 </t>
   </si>
   <si>
-    <t>Who's involved in plan?</t>
-  </si>
-  <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
+    <t>執行照護工作的團隊</t>
+  </si>
+  <si>
+    <t>確定負責執行此照護計畫的照護團隊。</t>
   </si>
   <si>
     <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
@@ -1258,10 +1254,7 @@
     <t>照顧計畫對應的需求，即這個照顧計畫是針對哪些問題或需求而設計的？</t>
   </si>
   <si>
-    <t>Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
-  </si>
-  <si>
-    <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
+    <t>本照護計畫試圖解決的健康問題(例如：疾病、病情、問題)。</t>
   </si>
   <si>
     <t>Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
@@ -1303,7 +1296,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1433,7 +1426,7 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1492,11 +1485,7 @@
     <t>照顧計畫的活動參考 Resource。</t>
   </si>
   <si>
-    <t>The details of the proposed activity represented in a specific resource.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  -The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
+    <t>包含照護計畫之照護行動(診斷、治療等)明細的 request/request-like 資源。</t>
   </si>
   <si>
     <t>Details in a form consistent with other applications and contexts of use.</t>
@@ -1557,7 +1546,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1591,7 +1580,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1618,7 +1607,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1631,10 +1620,10 @@
 </t>
   </si>
   <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+    <t>為何需要此行動</t>
+  </si>
+  <si>
+    <t>指出為何此行動是此照護計畫的一部分。</t>
   </si>
   <si>
     <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
@@ -1643,7 +1632,7 @@
     <t>CarePlan.activity.detail.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1756,13 +1745,10 @@
 </t>
   </si>
   <si>
-    <t>Where it should happen</t>
-  </si>
-  <si>
-    <t>Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
-  </si>
-  <si>
-    <t>May reference a specific clinical location or may identify a type of location.</t>
+    <t>行動發生的地點</t>
+  </si>
+  <si>
+    <t>預期要執行此行動的地點。</t>
   </si>
   <si>
     <t>Helps in planning of activity.</t>
@@ -1781,13 +1767,10 @@
 </t>
   </si>
   <si>
-    <t>Who will be responsible?</t>
-  </si>
-  <si>
-    <t>Identifies who's expected to be involved in the activity.</t>
-  </si>
-  <si>
-    <t>A performer MAY also be a participant in the care plan.</t>
+    <t>執行或提供此行動的人員</t>
+  </si>
+  <si>
+    <t>確定預期要執行此行動的特定人員或組織。</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1803,7 +1786,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>What is to be administered/supplied</t>
@@ -1815,7 +1798,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1838,6 +1821,12 @@
 </t>
   </si>
   <si>
+    <t>物料/主題/產品資訊要參照的資源</t>
+  </si>
+  <si>
+    <t>辨識行動所涉及的物料/主題/產品。</t>
+  </si>
+  <si>
     <t>CarePlan.activity.detail.dailyAmount</t>
   </si>
   <si>
@@ -1845,7 +1834,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2889,7 +2878,7 @@
         <v>20</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>20</v>
@@ -2901,13 +2890,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2925,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2954,14 +2943,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2980,16 +2969,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3039,7 +3028,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -3057,7 +3046,7 @@
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -3068,10 +3057,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3094,13 +3083,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -3151,7 +3140,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -3169,7 +3158,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -3180,14 +3169,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3206,16 +3195,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3253,19 +3242,19 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3277,13 +3266,13 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>20</v>
@@ -3294,10 +3283,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3323,10 +3312,10 @@
         <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3353,13 +3342,13 @@
         <v>20</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>20</v>
@@ -3377,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>87</v>
@@ -3395,7 +3384,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>20</v>
@@ -3406,10 +3395,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3432,16 +3421,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3491,7 +3480,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>87</v>
@@ -3503,13 +3492,13 @@
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -3520,14 +3509,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3546,16 +3535,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3605,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3623,7 +3612,7 @@
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -3634,14 +3623,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3660,16 +3649,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3719,7 +3708,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3731,13 +3720,13 @@
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>20</v>
@@ -3748,14 +3737,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3774,19 +3763,19 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3835,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3847,13 +3836,13 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
@@ -3864,10 +3853,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3890,19 +3879,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3951,7 +3940,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3966,24 +3955,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4006,13 +3995,13 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4063,7 +4052,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4078,10 +4067,10 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -4092,10 +4081,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4121,13 +4110,13 @@
         <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4177,7 +4166,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4192,10 +4181,10 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -4206,14 +4195,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4232,17 +4221,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4291,7 +4282,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4306,7 +4297,7 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
@@ -4320,10 +4311,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4346,13 +4337,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4403,7 +4394,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4421,7 +4412,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4432,14 +4423,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4458,16 +4449,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4505,19 +4496,19 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4529,13 +4520,13 @@
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -4546,10 +4537,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4572,16 +4563,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4631,7 +4622,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4640,7 +4631,7 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>99</v>
@@ -4649,7 +4640,7 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -4660,10 +4651,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4689,13 +4680,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4721,13 +4712,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4745,7 +4736,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4763,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -4774,10 +4765,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4800,16 +4791,16 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4859,7 +4850,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4877,7 +4868,7 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4888,10 +4879,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4914,16 +4905,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4973,7 +4964,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4991,7 +4982,7 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -5002,14 +4993,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5028,19 +5019,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5089,7 +5080,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5104,7 +5095,7 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -5118,10 +5109,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5144,13 +5135,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5201,7 +5192,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5219,7 +5210,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -5230,14 +5221,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5256,16 +5247,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5303,19 +5294,19 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5327,13 +5318,13 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -5344,10 +5335,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5370,16 +5361,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5429,7 +5420,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5438,7 +5429,7 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
@@ -5447,7 +5438,7 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5458,10 +5449,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5487,13 +5478,13 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5519,13 +5510,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5543,7 +5534,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5561,7 +5552,7 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5572,10 +5563,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5598,16 +5589,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5657,7 +5648,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5675,7 +5666,7 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -5686,10 +5677,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5712,16 +5703,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5771,7 +5762,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5789,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5800,10 +5791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5826,16 +5817,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5885,7 +5876,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5940,13 +5931,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5997,7 +5988,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6015,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -6033,7 +6024,7 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6052,16 +6043,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6099,19 +6090,19 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6123,13 +6114,13 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -6166,16 +6157,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6225,7 +6216,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6234,7 +6225,7 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
@@ -6243,7 +6234,7 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -6283,13 +6274,13 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6315,13 +6306,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6339,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6357,7 +6348,7 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -6394,16 +6385,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6453,7 +6444,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6471,7 +6462,7 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -6508,16 +6499,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6567,7 +6558,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6585,7 +6576,7 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
@@ -6634,7 +6625,7 @@
         <v>253</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6659,13 +6650,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6698,24 +6689,24 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6741,16 +6732,16 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6775,13 +6766,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6799,7 +6790,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6814,7 +6805,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6828,10 +6819,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6854,19 +6845,19 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6891,29 +6882,29 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6934,7 +6925,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6942,13 +6933,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
@@ -6970,19 +6961,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6992,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>20</v>
@@ -7007,13 +6998,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7031,7 +7022,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7052,7 +7043,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7060,10 +7051,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7086,13 +7077,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7143,7 +7134,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7172,10 +7163,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7198,17 +7189,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7257,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7278,7 +7269,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7286,14 +7277,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7312,17 +7303,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7371,7 +7362,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7386,24 +7377,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7426,13 +7417,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7483,7 +7474,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7501,7 +7492,7 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7512,14 +7503,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7538,16 +7529,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7585,19 +7576,19 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7609,13 +7600,13 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7626,10 +7617,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7652,16 +7643,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7711,7 +7702,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7720,7 +7711,7 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
@@ -7729,7 +7720,7 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7740,10 +7731,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7769,13 +7760,13 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7801,13 +7792,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7825,7 +7816,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7843,7 +7834,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7854,10 +7845,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7880,16 +7871,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7939,7 +7930,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7957,7 +7948,7 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7968,10 +7959,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7994,16 +7985,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8053,7 +8044,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8071,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -8082,10 +8073,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8108,16 +8099,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8167,7 +8158,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8182,24 +8173,24 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8222,13 +8213,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8279,7 +8270,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8297,7 +8288,7 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -8308,14 +8299,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8334,16 +8325,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8381,19 +8372,19 @@
         <v>20</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8405,13 +8396,13 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -8422,10 +8413,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8448,16 +8439,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8507,7 +8498,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8516,7 +8507,7 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
@@ -8525,7 +8516,7 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8536,10 +8527,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8565,13 +8556,13 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8597,13 +8588,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8621,7 +8612,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8639,7 +8630,7 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8650,10 +8641,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8676,16 +8667,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8735,7 +8726,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8753,7 +8744,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8764,10 +8755,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8790,16 +8781,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8849,7 +8840,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8867,7 +8858,7 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
@@ -8878,14 +8869,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8904,19 +8895,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8965,7 +8956,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8980,24 +8971,24 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9020,13 +9011,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9077,7 +9068,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9095,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -9106,14 +9097,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9132,16 +9123,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9179,19 +9170,19 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9203,13 +9194,13 @@
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -9220,10 +9211,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9246,16 +9237,16 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9305,7 +9296,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9314,7 +9305,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -9323,21 +9314,21 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9360,23 +9351,23 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>20</v>
@@ -9421,7 +9412,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9430,7 +9421,7 @@
         <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>99</v>
@@ -9439,25 +9430,25 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9476,13 +9467,13 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9533,7 +9524,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9548,13 +9539,13 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9562,10 +9553,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9588,16 +9579,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>366</v>
+        <v>197</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9647,7 +9638,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9702,13 +9693,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9759,7 +9750,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9777,7 +9768,7 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9795,7 +9786,7 @@
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9814,16 +9805,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9861,19 +9852,19 @@
         <v>20</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9885,13 +9876,13 @@
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9928,16 +9919,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>372</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9987,7 +9978,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9996,7 +9987,7 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>99</v>
@@ -10005,7 +9996,7 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -10045,13 +10036,13 @@
         <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10077,13 +10068,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10101,7 +10092,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10119,7 +10110,7 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -10156,16 +10147,16 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10215,7 +10206,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10233,7 +10224,7 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
@@ -10270,16 +10261,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10329,7 +10320,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10347,7 +10338,7 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
@@ -10384,7 +10375,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>377</v>
@@ -10393,7 +10384,7 @@
         <v>378</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>379</v>
+        <v>197</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10472,10 +10463,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10498,13 +10489,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10555,7 +10546,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10573,7 +10564,7 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
@@ -10584,14 +10575,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10610,16 +10601,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10657,19 +10648,19 @@
         <v>20</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10681,13 +10672,13 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10698,10 +10689,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10724,16 +10715,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10783,7 +10774,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10792,7 +10783,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -10801,7 +10792,7 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
@@ -10812,10 +10803,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10841,13 +10832,13 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10873,13 +10864,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10897,7 +10888,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10915,7 +10906,7 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
@@ -10926,10 +10917,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10952,16 +10943,16 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11011,7 +11002,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11029,7 +11020,7 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
@@ -11040,10 +11031,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11066,16 +11057,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11125,7 +11116,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11143,7 +11134,7 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
@@ -11154,10 +11145,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11180,17 +11171,19 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11239,7 +11232,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11254,13 +11247,13 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
@@ -11268,10 +11261,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11294,19 +11287,19 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O80" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11355,7 +11348,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11370,24 +11363,24 @@
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11410,13 +11403,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11467,7 +11460,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11485,7 +11478,7 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
@@ -11496,14 +11489,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11522,16 +11515,16 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11569,19 +11562,19 @@
         <v>20</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11593,13 +11586,13 @@
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>20</v>
@@ -11610,10 +11603,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11636,16 +11629,16 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11695,7 +11688,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11704,7 +11697,7 @@
         <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>99</v>
@@ -11713,7 +11706,7 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>20</v>
@@ -11724,10 +11717,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11753,13 +11746,13 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11785,13 +11778,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -11809,7 +11802,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11827,7 +11820,7 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>20</v>
@@ -11838,10 +11831,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11864,16 +11857,16 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11923,7 +11916,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11941,7 +11934,7 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>20</v>
@@ -11952,10 +11945,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11978,16 +11971,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12037,7 +12030,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12055,7 +12048,7 @@
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>20</v>
@@ -12066,10 +12059,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12092,19 +12085,19 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12153,7 +12146,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12168,7 +12161,7 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>20</v>
@@ -12182,10 +12175,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12208,19 +12201,19 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12269,7 +12262,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12287,21 +12280,21 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12324,13 +12317,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12381,7 +12374,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12399,7 +12392,7 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>20</v>
@@ -12410,14 +12403,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12436,16 +12429,16 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12483,19 +12476,19 @@
         <v>20</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12507,13 +12500,13 @@
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
@@ -12524,10 +12517,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12550,16 +12543,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12609,7 +12602,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12618,7 +12611,7 @@
         <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>99</v>
@@ -12627,7 +12620,7 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>20</v>
@@ -12638,10 +12631,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12667,13 +12660,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12699,13 +12692,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -12723,7 +12716,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12741,7 +12734,7 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>20</v>
@@ -12752,10 +12745,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12778,16 +12771,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12837,7 +12830,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12855,7 +12848,7 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>20</v>
@@ -12866,10 +12859,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12892,16 +12885,16 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12951,7 +12944,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12969,7 +12962,7 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>20</v>
@@ -12980,10 +12973,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13006,17 +12999,17 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13065,7 +13058,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13077,13 +13070,13 @@
         <v>20</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -13094,10 +13087,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13120,13 +13113,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13177,7 +13170,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13195,7 +13188,7 @@
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>20</v>
@@ -13206,14 +13199,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13232,16 +13225,16 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13291,7 +13284,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13303,13 +13296,13 @@
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>20</v>
@@ -13320,14 +13313,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13346,19 +13339,19 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13407,7 +13400,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13419,13 +13412,13 @@
         <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>20</v>
@@ -13436,10 +13429,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13462,16 +13455,16 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13497,13 +13490,13 @@
         <v>20</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -13521,7 +13514,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13550,10 +13543,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13576,19 +13569,19 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -13637,7 +13630,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13652,10 +13645,10 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>20</v>
@@ -13666,10 +13659,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13692,19 +13685,19 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -13753,7 +13746,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13771,21 +13764,21 @@
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13808,19 +13801,19 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -13869,7 +13862,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13878,16 +13871,16 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>20</v>
@@ -13898,10 +13891,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13924,17 +13917,17 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -13983,7 +13976,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13992,7 +13985,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14001,7 +13994,7 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>20</v>
@@ -14012,10 +14005,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14038,13 +14031,13 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14095,7 +14088,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14113,7 +14106,7 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>20</v>
@@ -14124,14 +14117,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14150,16 +14143,16 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14209,7 +14202,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14221,13 +14214,13 @@
         <v>20</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>20</v>
@@ -14238,14 +14231,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14264,19 +14257,19 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>20</v>
@@ -14325,7 +14318,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14337,13 +14330,13 @@
         <v>20</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>20</v>
@@ -14354,10 +14347,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14383,14 +14376,14 @@
         <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -14415,13 +14408,13 @@
         <v>20</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14439,7 +14432,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14457,7 +14450,7 @@
         <v>20</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>20</v>
@@ -14468,10 +14461,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14494,17 +14487,17 @@
         <v>20</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>20</v>
@@ -14553,7 +14546,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14568,10 +14561,10 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>20</v>
@@ -14582,10 +14575,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14611,16 +14604,16 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -14669,7 +14662,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14684,10 +14677,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>20</v>
@@ -14698,10 +14691,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14724,19 +14717,19 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -14761,13 +14754,13 @@
         <v>20</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>20</v>
@@ -14785,7 +14778,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14800,24 +14793,24 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14840,16 +14833,16 @@
         <v>20</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14875,13 +14868,13 @@
         <v>20</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -14899,7 +14892,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14914,7 +14907,7 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>20</v>
@@ -14928,10 +14921,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14954,16 +14947,16 @@
         <v>20</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15013,7 +15006,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15028,7 +15021,7 @@
         <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>20</v>
@@ -15042,10 +15035,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15068,17 +15061,17 @@
         <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -15127,7 +15120,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15145,7 +15138,7 @@
         <v>20</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>20</v>
@@ -15156,10 +15149,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15185,16 +15178,16 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O114" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -15219,13 +15212,13 @@
         <v>20</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>20</v>
@@ -15243,7 +15236,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>87</v>
@@ -15258,24 +15251,24 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15298,16 +15291,16 @@
         <v>20</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15357,7 +15350,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15372,7 +15365,7 @@
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>20</v>
@@ -15386,10 +15379,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15412,26 +15405,26 @@
         <v>20</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="P116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q116" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="N116" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q116" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="R116" t="s" s="2">
         <v>20</v>
       </c>
@@ -15475,7 +15468,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15490,10 +15483,10 @@
         <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>20</v>
@@ -15504,10 +15497,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15530,17 +15523,17 @@
         <v>20</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15589,7 +15582,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15604,24 +15597,24 @@
         <v>99</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15644,19 +15637,19 @@
         <v>20</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O118" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15705,7 +15698,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15723,21 +15716,21 @@
         <v>20</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15760,19 +15753,19 @@
         <v>20</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>567</v>
+        <v>197</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>20</v>
@@ -15821,7 +15814,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15836,24 +15829,24 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15876,13 +15869,13 @@
         <v>20</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15909,29 +15902,29 @@
         <v>20</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15949,24 +15942,24 @@
         <v>20</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>20</v>
@@ -15988,15 +15981,17 @@
         <v>20</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>20</v>
@@ -16045,7 +16040,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16063,25 +16058,25 @@
         <v>20</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16100,17 +16095,17 @@
         <v>20</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -16159,7 +16154,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16177,21 +16172,21 @@
         <v>20</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16214,13 +16209,13 @@
         <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16271,7 +16266,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16289,21 +16284,21 @@
         <v>20</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16326,13 +16321,13 @@
         <v>20</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16383,7 +16378,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16401,21 +16396,21 @@
         <v>20</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16438,17 +16433,17 @@
         <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16497,7 +16492,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16512,16 +16507,16 @@
         <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCarePlan.xlsx
+++ b/docs/StructureDefinition-LTCCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
